--- a/docs/Master.xlsx
+++ b/docs/Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\spashikanti\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6264D188-C6BC-4D04-99E8-98F0BC14D236}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{692E7858-4AA8-4AAB-B5CF-657E84948C5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{688F1374-0EC1-4E8E-BFFA-7F996D194E82}"/>
   </bookViews>
@@ -123,8 +123,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{6E94CD09-7B57-45D1-90BB-0BCFEE92826E}" name="Table1" displayName="Table1" ref="A1:E4" totalsRowShown="0">
-  <autoFilter ref="A1:E4" xr:uid="{6E94CD09-7B57-45D1-90BB-0BCFEE92826E}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{6E94CD09-7B57-45D1-90BB-0BCFEE92826E}" name="Table1" displayName="Table1" ref="A1:E2" totalsRowShown="0">
+  <autoFilter ref="A1:E2" xr:uid="{6E94CD09-7B57-45D1-90BB-0BCFEE92826E}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{832BB437-7652-41FF-87A1-BE677D8409BD}" name="Date" dataDxfId="0"/>
     <tableColumn id="2" xr3:uid="{B245DC16-90D7-4C87-9547-4649FF995AE5}" name="Merchant"/>
@@ -453,7 +453,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18B58FB5-32A4-43EA-AEC4-9B98FD9F2F24}">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="14.33203125" bestFit="1" customWidth="1"/>
@@ -484,14 +484,6 @@
       <c r="A2" s="3"/>
       <c r="C2" s="2"/>
     </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="3"/>
-      <c r="C3" s="2"/>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="3"/>
-      <c r="C4" s="2"/>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
